--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,13 +647,10 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
@@ -1385,193 +1382,6 @@
     <t>TEL</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>emailType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType}
-</t>
-  </si>
-  <si>
-    <t>Type of email | type de messagerie électronique</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.system</t>
-  </si>
-  <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system</t>
-  </si>
-  <si>
-    <t>ContactPoint.system</t>
-  </si>
-  <si>
-    <t>ele-1
-cpt-2</t>
-  </si>
-  <si>
-    <t>XTN.3</t>
-  </si>
-  <si>
-    <t>./scheme</t>
-  </si>
-  <si>
-    <t>./ContactPointType</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
-  </si>
-  <si>
-    <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
-  </si>
-  <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
-  </si>
-  <si>
-    <t>ContactPoint.value</t>
-  </si>
-  <si>
-    <t>XTN.1 (or XTN.12)</t>
-  </si>
-  <si>
-    <t>./url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | mobile - purpose of this contact point</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for the contact point.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
-  </si>
-  <si>
-    <t>Use of contact point.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use</t>
-  </si>
-  <si>
-    <t>ContactPoint.use</t>
-  </si>
-  <si>
-    <t>XTN.2 - but often indicated by field</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./ContactPointPurpose</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
-  </si>
-  <si>
-    <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.</t>
-  </si>
-  <si>
-    <t>ContactPoint.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.period</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
-  </si>
-  <si>
-    <t>ContactPoint.period</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime</t>
   </si>
   <si>
@@ -1621,6 +1431,9 @@
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>The days of the week.</t>
@@ -2046,10 +1859,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN87"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.05859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4182,9 +3995,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4262,13 +4073,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4290,13 +4101,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4376,13 +4187,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4404,13 +4215,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4490,10 +4301,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4519,16 +4330,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4577,7 +4388,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4606,10 +4417,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4632,17 +4443,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4679,10 +4490,10 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
@@ -4691,7 +4502,7 @@
         <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4706,27 +4517,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4748,17 +4559,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4807,7 +4618,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4822,24 +4633,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4948,10 +4759,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5062,10 +4873,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5091,16 +4902,16 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5125,31 +4936,31 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5167,7 +4978,7 @@
         <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5178,10 +4989,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5204,19 +5015,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5244,28 +5055,28 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5280,10 +5091,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5294,10 +5105,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5323,16 +5134,16 @@
         <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5342,46 +5153,46 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5396,13 +5207,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5410,10 +5221,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5439,13 +5250,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5459,43 +5270,43 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5510,13 +5321,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5524,10 +5335,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5550,16 +5361,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5609,7 +5420,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5621,16 +5432,16 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5638,10 +5449,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5664,16 +5475,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5723,7 +5534,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5735,16 +5546,16 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5752,13 +5563,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5780,17 +5591,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5839,7 +5650,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5854,24 +5665,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5980,10 +5791,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6094,10 +5905,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6123,16 +5934,16 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6157,31 +5968,31 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6199,7 +6010,7 @@
         <v>102</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6210,10 +6021,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6236,19 +6047,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6276,28 +6087,28 @@
         <v>153</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6312,10 +6123,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6326,10 +6137,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6355,16 +6166,16 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6374,46 +6185,46 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6428,13 +6239,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6442,10 +6253,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6471,13 +6282,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6491,43 +6302,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6542,13 +6353,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6556,10 +6367,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6582,16 +6393,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6641,7 +6452,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6653,16 +6464,16 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6670,10 +6481,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6696,16 +6507,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6755,7 +6566,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6767,16 +6578,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6784,10 +6595,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6810,26 +6621,26 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O42" t="s" s="2">
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6873,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6888,24 +6699,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6928,19 +6739,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6989,7 +6800,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7001,27 +6812,27 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7130,10 +6941,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7244,10 +7055,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7270,16 +7081,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7329,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7338,16 +7149,16 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7358,10 +7169,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7384,68 +7195,68 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7454,16 +7265,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7474,10 +7285,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7500,16 +7311,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7559,7 +7370,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7571,13 +7382,13 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7588,10 +7399,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7614,16 +7425,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7673,7 +7484,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7685,13 +7496,13 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7702,10 +7513,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7728,19 +7539,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7768,16 +7579,16 @@
         <v>163</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7787,7 +7598,7 @@
         <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7802,13 +7613,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7816,13 +7627,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -7844,19 +7655,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7881,11 +7692,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7903,7 +7714,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7918,13 +7729,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7932,13 +7743,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -7960,19 +7771,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7997,11 +7808,11 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8019,7 +7830,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8034,13 +7845,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8048,13 +7859,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8076,19 +7887,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8113,11 +7924,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8135,7 +7946,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8150,13 +7961,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8164,13 +7975,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8192,19 +8003,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8229,11 +8040,11 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8251,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8266,13 +8077,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8280,13 +8091,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8308,19 +8119,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8345,11 +8156,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8367,7 +8178,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8382,13 +8193,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8396,13 +8207,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8424,19 +8235,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8461,11 +8272,11 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8483,7 +8294,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8498,13 +8309,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8512,13 +8323,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8540,19 +8351,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8577,11 +8388,11 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8599,7 +8410,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8614,13 +8425,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8628,10 +8439,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8654,16 +8465,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8692,11 +8503,11 @@
         <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8713,7 +8524,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8728,13 +8539,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8742,10 +8553,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8768,16 +8579,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8827,7 +8638,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8839,27 +8650,27 @@
         <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8882,16 +8693,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8941,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8953,13 +8764,13 @@
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8970,10 +8781,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8996,17 +8807,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9043,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
@@ -9053,7 +8864,7 @@
         <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9065,16 +8876,16 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9082,13 +8893,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9110,17 +8921,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9169,7 +8980,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9181,16 +8992,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9198,10 +9009,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9212,10 +9023,10 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
@@ -9224,15 +9035,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>105</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9281,25 +9094,25 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9310,21 +9123,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9336,17 +9149,15 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9383,37 +9194,37 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9424,14 +9235,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>110</v>
       </c>
@@ -9440,7 +9249,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9452,13 +9261,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>447</v>
+        <v>112</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
+        <v>113</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>114</v>
@@ -9499,16 +9308,16 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>118</v>
@@ -9540,44 +9349,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I66" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9625,7 +9436,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>451</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9643,7 +9454,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9654,10 +9465,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9665,10 +9476,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9677,19 +9488,19 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9700,7 +9511,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9715,13 +9526,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9739,28 +9550,28 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>463</v>
+        <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9768,10 +9579,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9779,35 +9590,31 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9855,7 +9662,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9870,13 +9677,13 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>474</v>
+        <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9884,10 +9691,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9904,26 +9711,24 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>173</v>
+        <v>462</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9947,13 +9752,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>483</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9971,7 +9776,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9986,13 +9791,13 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>485</v>
+        <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>487</v>
+        <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10000,10 +9805,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10023,19 +9828,19 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10085,7 +9890,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10100,10 +9905,10 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>108</v>
+        <v>444</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10114,10 +9919,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10128,29 +9933,27 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>284</v>
+        <v>440</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10199,28 +10002,28 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>500</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10228,10 +10031,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>501</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>501</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10242,10 +10045,10 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
@@ -10254,17 +10057,15 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>502</v>
+        <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>503</v>
+        <v>105</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10313,25 +10114,25 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>506</v>
+        <v>108</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -10342,21 +10143,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10368,15 +10169,17 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10413,37 +10216,37 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10454,14 +10257,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>110</v>
+        <v>448</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10474,24 +10277,26 @@
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>112</v>
+        <v>449</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10527,19 +10332,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>118</v>
+        <v>451</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10568,46 +10373,44 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>510</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>511</v>
+        <v>476</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>512</v>
+        <v>477</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10655,25 +10458,25 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10684,10 +10487,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10698,7 +10501,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -10710,16 +10513,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>458</v>
+        <v>286</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10745,13 +10548,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>518</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10769,25 +10572,25 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>506</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10798,10 +10601,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10815,7 +10618,7 @@
         <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
@@ -10824,15 +10627,17 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10881,7 +10686,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10899,7 +10704,7 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>506</v>
+        <v>444</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10910,10 +10715,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10924,10 +10729,10 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>77</v>
@@ -10936,18 +10741,20 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10995,1061 +10802,35 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN87">
+  <autoFilter ref="A1:AN78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12059,7 +10840,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI86">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="492">
   <si>
     <t>Property</t>
   </si>
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
@@ -1333,7 +1333,7 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interopsante.org/fhir/StructureDefinition/FrContactPoint}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -1377,6 +1377,10 @@
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+  </si>
+  <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>TEL</t>
@@ -8992,13 +8996,13 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>430</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>432</v>
@@ -9009,10 +9013,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9035,16 +9039,16 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9094,7 +9098,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9112,7 +9116,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9123,10 +9127,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9235,10 +9239,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9349,14 +9353,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9378,10 +9382,10 @@
         <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>114</v>
@@ -9436,7 +9440,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9465,10 +9469,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9494,13 +9498,13 @@
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9529,10 +9533,10 @@
         <v>243</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9550,7 +9554,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9568,7 +9572,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9579,10 +9583,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9608,10 +9612,10 @@
         <v>316</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9662,7 +9666,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9680,7 +9684,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9691,10 +9695,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9717,16 +9721,16 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9776,7 +9780,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9794,7 +9798,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9805,10 +9809,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9831,16 +9835,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9890,7 +9894,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9908,7 +9912,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9919,10 +9923,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9945,13 +9949,13 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10002,7 +10006,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10020,7 +10024,7 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -10031,10 +10035,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10143,10 +10147,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10257,14 +10261,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10286,10 +10290,10 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
@@ -10344,7 +10348,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10373,10 +10377,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10402,13 +10406,13 @@
         <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10458,7 +10462,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -10487,10 +10491,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10516,10 +10520,10 @@
         <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>286</v>
@@ -10572,7 +10576,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10587,10 +10591,10 @@
         <v>288</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10601,10 +10605,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10630,13 +10634,13 @@
         <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10686,7 +10690,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10704,7 +10708,7 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10715,10 +10719,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10741,19 +10745,19 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>356</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10802,7 +10806,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10820,7 +10824,7 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$88</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2862" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role-exercice</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -322,321 +322,347 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>PractitionerRole.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>PractitionerRole.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>PractitionerRole.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>PractitionerRole.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:serviceTypeDuration</t>
+  </si>
+  <si>
+    <t>serviceTypeDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration}
+</t>
+  </si>
+  <si>
+    <t>FR Core Service Type Duration Extension</t>
+  </si>
+  <si>
+    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.extension:as-ext-data-trace</t>
-  </si>
-  <si>
-    <t>as-ext-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
-</t>
-  </si>
-  <si>
-    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>PractitionerRole.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>PractitionerRole.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>PractitionerRole.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>PractitionerRole.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>PractitionerRole.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-contracted</t>
   </si>
   <si>
@@ -736,30 +762,12 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice</t>
-  </si>
-  <si>
-    <t>idSituationExercice</t>
-  </si>
-  <si>
-    <t>Identifiant d'activité propre au RPPS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.id</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.use</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.use</t>
   </si>
   <si>
@@ -788,9 +796,6 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.type</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.type</t>
@@ -824,16 +829,14 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.system</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>The namespace for the identifier value | Namespace du RASS)</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.
+Namespace du RASS)</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -842,9 +845,6 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
-  </si>
-  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -860,9 +860,6 @@
     <t>./IdentifierType</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.value</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.value</t>
   </si>
   <si>
@@ -888,9 +885,6 @@
   </si>
   <si>
     <t>./Value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.period</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.period</t>
@@ -906,17 +900,9 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>CX.7 + CX.8</t>
   </si>
   <si>
@@ -924,9 +910,6 @@
   </si>
   <si>
     <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.assigner</t>
@@ -948,10 +931,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
@@ -959,6 +938,42 @@
   </si>
   <si>
     <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice</t>
+  </si>
+  <si>
+    <t>idSituationExercice</t>
+  </si>
+  <si>
+    <t>Identifiant d'activité propre au RPPS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+  </si>
+  <si>
+    <t>http://rpps.fr</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.period</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm</t>
@@ -1115,7 +1130,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner)
 </t>
   </si>
   <si>
@@ -1125,16 +1140,13 @@
     <t>Practitioner that is able to provide the defined services for the organization.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>.player</t>
   </si>
   <si>
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1150,7 +1162,7 @@
     <t>PractitionerRole.code</t>
   </si>
   <si>
-    <t>Roles which this practitioner may perform</t>
+    <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
     <t>Roles which this practitioner is authorized to perform for the organization.</t>
@@ -1162,10 +1174,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>The role a person plays representing an organization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/practitioner-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1265,19 +1274,13 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t>Specific specialty of the practitioner</t>
+    <t>Specific specialty associated with the organization | spécialité ordinale du professionnel de santé au sein de l'organisation</t>
   </si>
   <si>
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>Specific specialty associated with the agency.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1292,7 +1295,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
@@ -1314,7 +1317,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service)
 </t>
   </si>
   <si>
@@ -1337,10 +1340,10 @@
 </t>
   </si>
   <si>
-    <t>Contact details that are specific to the role/location/service</t>
-  </si>
-  <si>
-    <t>Contact details that are specific to the role/location/service.</t>
+    <t>Details of a Technology mediated contact point | Coordonnées électroniques détaillées</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
@@ -1350,14 +1353,14 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>XTN</t>
   </si>
   <si>
-    <t>.telecom</t>
+    <t>TEL</t>
   </si>
   <si>
     <t>ContactPoint</t>
@@ -1376,16 +1379,6 @@
     <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (BoiteLettreMSS).</t>
   </si>
   <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
-  </si>
-  <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime</t>
   </si>
   <si>
@@ -1437,9 +1430,6 @@
     <t>Indicates which days of the week are available between the start and end Times.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>The days of the week.</t>
   </si>
   <si>
@@ -1514,9 +1504,6 @@
   </si>
   <si>
     <t>Service is not available (seasonally or for a public holiday) from this date.</t>
-  </si>
-  <si>
-    <t>DR</t>
   </si>
   <si>
     <t>PractitionerRole.availabilityExceptions</t>
@@ -1544,9 +1531,6 @@
     <t>Organizations have multiple systems that provide various services and ,ay also be different for practitioners too.  So the endpoint satisfies the need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN78"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
@@ -2349,16 +2333,16 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2369,10 +2353,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2395,13 +2379,13 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2452,7 +2436,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2470,7 +2454,7 @@
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2481,14 +2465,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2507,16 +2491,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2554,19 +2538,19 @@
         <v>77</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2575,16 +2559,16 @@
         <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2595,13 +2579,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>77</v>
@@ -2623,13 +2607,13 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2680,7 +2664,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2689,10 +2673,10 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2709,10 +2693,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2738,13 +2722,13 @@
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2794,7 +2778,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2803,16 +2787,16 @@
         <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2823,10 +2807,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2849,16 +2833,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2908,7 +2892,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2917,16 +2901,16 @@
         <v>88</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2937,10 +2921,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2963,16 +2947,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3022,7 +3006,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3031,16 +3015,16 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -3051,10 +3035,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3077,16 +3061,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3124,16 +3108,16 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>147</v>
@@ -3145,16 +3129,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -3168,9 +3152,11 @@
         <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3179,7 +3165,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -3191,16 +3177,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3211,7 +3197,7 @@
         <v>77</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>77</v>
@@ -3226,13 +3212,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3250,7 +3236,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3259,16 +3245,16 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3279,10 +3265,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3305,16 +3291,16 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3340,13 +3326,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3364,7 +3350,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3373,16 +3359,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3393,10 +3379,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3407,28 +3393,28 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3454,13 +3440,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3478,25 +3464,25 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3507,10 +3493,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3527,22 +3513,22 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3568,13 +3554,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3592,7 +3578,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3601,16 +3587,16 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3621,14 +3607,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3647,16 +3633,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3682,13 +3668,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3706,7 +3692,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3715,16 +3701,16 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3735,21 +3721,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3761,16 +3747,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3820,25 +3806,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3849,14 +3835,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3875,16 +3861,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3922,19 +3908,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3943,16 +3929,16 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3963,14 +3949,12 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3979,10 +3963,10 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
@@ -3991,13 +3975,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4036,19 +4020,17 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4057,10 +4039,10 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -4077,13 +4059,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4093,10 +4075,10 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -4105,13 +4087,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4162,7 +4144,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4171,10 +4153,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -4191,13 +4173,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4219,13 +4201,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4276,7 +4258,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4285,10 +4267,10 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -4305,33 +4287,35 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>215</v>
@@ -4339,12 +4323,8 @@
       <c r="M22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4380,19 +4360,19 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4401,16 +4381,16 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4421,12 +4401,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4435,7 +4417,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>89</v>
@@ -4444,21 +4426,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4494,19 +4474,19 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4515,36 +4495,34 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4557,23 +4535,25 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4622,7 +4602,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4631,30 +4611,30 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4665,28 +4645,30 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4722,62 +4704,62 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>107</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>108</v>
+        <v>235</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4789,17 +4771,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4836,37 +4816,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4877,46 +4857,44 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4940,49 +4918,49 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>116</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4993,10 +4971,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5013,25 +4991,25 @@
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5056,13 +5034,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5080,7 +5058,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5089,16 +5067,16 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5109,10 +5087,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5120,7 +5098,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -5135,19 +5113,19 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5157,10 +5135,10 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -5172,13 +5150,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5196,7 +5174,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5205,19 +5183,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>270</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5225,10 +5203,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5251,18 +5229,20 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5274,7 +5254,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5310,7 +5290,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5319,19 +5299,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5339,10 +5319,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5365,16 +5345,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5388,7 +5368,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5424,7 +5404,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5433,19 +5413,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5453,10 +5433,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5479,17 +5459,15 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5538,7 +5516,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5547,19 +5525,19 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK32" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5567,14 +5545,12 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5583,7 +5559,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5595,18 +5571,18 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5654,41 +5630,43 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>229</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5697,7 +5675,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5706,19 +5684,21 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5766,50 +5746,50 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>107</v>
+        <v>227</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>108</v>
+        <v>235</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5821,17 +5801,15 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5868,37 +5846,37 @@
         <v>77</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5909,46 +5887,44 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5972,49 +5948,49 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>246</v>
+        <v>116</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6025,10 +6001,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6045,25 +6021,25 @@
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6088,13 +6064,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6112,7 +6088,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6121,16 +6097,16 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6141,10 +6117,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6152,7 +6128,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6167,19 +6143,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6189,10 +6165,10 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6204,13 +6180,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6228,7 +6204,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6237,19 +6213,19 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK38" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>270</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6257,10 +6233,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6268,7 +6244,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6283,18 +6259,20 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6303,10 +6281,10 @@
         <v>77</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6342,7 +6320,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6351,19 +6329,19 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6371,10 +6349,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6397,16 +6375,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6420,7 +6398,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6456,7 +6434,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6465,19 +6443,19 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6485,10 +6463,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6511,17 +6489,15 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6570,7 +6546,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6579,19 +6555,19 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK41" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6599,10 +6575,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6616,7 +6592,7 @@
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6625,26 +6601,22 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q42" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6688,7 +6660,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6697,32 +6669,34 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK42" t="s" s="2">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6731,10 +6705,10 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
@@ -6743,19 +6717,17 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6804,39 +6776,39 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AK43" t="s" s="2">
-        <v>329</v>
+        <v>234</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>330</v>
+        <v>235</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>331</v>
+        <v>236</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>332</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6859,13 +6831,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6916,7 +6888,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6934,7 +6906,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6945,14 +6917,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>334</v>
+        <v>239</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6971,16 +6943,16 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7018,19 +6990,19 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AC45" t="s" s="2">
+      <c r="AF45" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7039,16 +7011,16 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7059,10 +7031,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>240</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7079,24 +7051,26 @@
         <v>77</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>336</v>
+        <v>173</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>337</v>
+        <v>241</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7120,13 +7094,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7144,7 +7118,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>340</v>
+        <v>248</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7153,16 +7127,16 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>342</v>
+        <v>196</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7173,10 +7147,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7199,24 +7173,24 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>252</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>253</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q47" t="s" s="2">
-        <v>348</v>
-      </c>
+      <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7236,13 +7210,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7260,7 +7234,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7269,16 +7243,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>350</v>
+        <v>259</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>351</v>
+        <v>249</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7289,10 +7263,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7300,13 +7274,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -7315,18 +7289,20 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>353</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>261</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
+        <v>262</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7335,10 +7311,10 @@
         <v>77</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>77</v>
@@ -7374,7 +7350,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7383,19 +7359,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7403,10 +7379,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7420,7 +7396,7 @@
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
@@ -7429,16 +7405,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>359</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>361</v>
+        <v>272</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7452,7 +7428,7 @@
         <v>77</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>77</v>
@@ -7488,7 +7464,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7497,19 +7473,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>362</v>
+        <v>277</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7517,10 +7493,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>279</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7531,7 +7507,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7543,20 +7519,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>364</v>
+        <v>281</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7580,50 +7552,52 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>283</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK50" t="s" s="2">
-        <v>371</v>
+        <v>284</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>372</v>
+        <v>285</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7631,14 +7605,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7650,7 +7622,7 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7659,20 +7631,18 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>289</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7696,11 +7666,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7718,28 +7690,28 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ51" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>293</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>294</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7747,14 +7719,12 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7775,24 +7745,26 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>250</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7812,11 +7784,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>380</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7834,43 +7808,41 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK52" t="s" s="2">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>77</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7891,19 +7863,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7928,11 +7898,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7950,43 +7922,41 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK53" t="s" s="2">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>77</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7998,29 +7968,25 @@
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>387</v>
+        <v>103</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8044,11 +8010,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8066,28 +8034,28 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>105</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8095,48 +8063,44 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>250</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>110</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>365</v>
+        <v>111</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8160,29 +8124,31 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>116</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8191,19 +8157,19 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>372</v>
+        <v>196</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8211,14 +8177,12 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8230,7 +8194,7 @@
         <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
@@ -8239,20 +8203,18 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>250</v>
+        <v>341</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>395</v>
+        <v>342</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8276,11 +8238,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8298,28 +8262,28 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8327,14 +8291,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8343,10 +8305,10 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>77</v>
@@ -8355,24 +8317,24 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>250</v>
+        <v>341</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="R57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8392,11 +8354,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8414,28 +8378,28 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK57" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8443,10 +8407,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8457,10 +8421,10 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>77</v>
@@ -8469,17 +8433,15 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>250</v>
+        <v>358</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>402</v>
+        <v>359</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8504,13 +8466,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8528,28 +8490,28 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK58" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>409</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8557,10 +8519,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8571,7 +8533,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>89</v>
@@ -8583,17 +8545,15 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>411</v>
+        <v>363</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8642,39 +8602,39 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>414</v>
+        <v>366</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>367</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>367</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8688,27 +8648,29 @@
         <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K60" t="s" s="2">
-        <v>418</v>
+        <v>251</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8732,31 +8694,27 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>417</v>
+        <v>367</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8765,19 +8723,19 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8785,12 +8743,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8799,7 +8759,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>89</v>
@@ -8811,17 +8771,19 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>424</v>
+        <v>251</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8846,29 +8808,29 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AC61" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8877,19 +8839,19 @@
         <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>429</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>432</v>
+        <v>336</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8897,13 +8859,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>434</v>
+        <v>381</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -8913,29 +8875,31 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>435</v>
+        <v>251</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8960,13 +8924,11 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8984,7 +8946,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8993,19 +8955,19 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>375</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>432</v>
+        <v>336</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9013,12 +8975,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9027,7 +8991,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>89</v>
@@ -9036,21 +9000,23 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>441</v>
+        <v>251</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>442</v>
+        <v>386</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>443</v>
+        <v>369</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9074,13 +9040,11 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9098,7 +9062,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>440</v>
+        <v>367</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9107,19 +9071,19 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9127,12 +9091,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9144,25 +9110,29 @@
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>251</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>105</v>
+        <v>390</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9186,13 +9156,11 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9210,28 +9178,28 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>107</v>
+        <v>367</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>108</v>
+        <v>375</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9239,44 +9207,48 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D65" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>112</v>
+        <v>394</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>113</v>
+        <v>369</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9300,31 +9272,29 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>118</v>
+        <v>367</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9333,19 +9303,19 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AK65" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9353,45 +9323,47 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="D66" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>450</v>
+        <v>398</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>451</v>
+        <v>369</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>114</v>
+        <v>370</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>217</v>
+        <v>371</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9416,13 +9388,11 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9440,7 +9410,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>452</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9449,19 +9419,19 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AK66" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9469,12 +9439,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9486,27 +9458,29 @@
         <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>455</v>
+        <v>369</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9530,13 +9504,11 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>458</v>
+        <v>403</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9554,7 +9526,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>453</v>
+        <v>367</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9563,19 +9535,19 @@
         <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9583,10 +9555,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>459</v>
+        <v>404</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>404</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9597,7 +9569,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9606,16 +9578,16 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>460</v>
+        <v>405</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>461</v>
+        <v>406</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9642,13 +9614,11 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9666,28 +9636,28 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>459</v>
+        <v>404</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK68" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9695,10 +9665,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9709,29 +9679,27 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9780,39 +9748,39 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9823,10 +9791,10 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
@@ -9835,17 +9803,15 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9894,25 +9860,25 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK70" t="s" s="2">
-        <v>77</v>
+        <v>422</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9923,10 +9889,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9949,16 +9915,18 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>471</v>
+        <v>426</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9994,19 +9962,17 @@
         <v>77</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="AC71" s="2"/>
       <c r="AD71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10015,19 +9981,19 @@
         <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>430</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>77</v>
+        <v>433</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10035,12 +10001,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>473</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10049,7 +10017,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10061,16 +10029,18 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>436</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>105</v>
+        <v>437</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10118,28 +10088,28 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>107</v>
+        <v>424</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>77</v>
+        <v>430</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>77</v>
+        <v>431</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>108</v>
+        <v>432</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>77</v>
+        <v>433</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10147,14 +10117,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10164,7 +10134,7 @@
         <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>77</v>
@@ -10173,16 +10143,16 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>111</v>
+        <v>439</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>112</v>
+        <v>440</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>113</v>
+        <v>441</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10220,19 +10190,19 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>438</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10241,16 +10211,16 @@
         <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ73" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>102</v>
+        <v>443</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10261,46 +10231,42 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>450</v>
+        <v>103</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10348,25 +10314,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>452</v>
+        <v>105</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10377,21 +10343,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10403,16 +10369,16 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>110</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>111</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>456</v>
+        <v>112</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10462,25 +10428,25 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>476</v>
+        <v>116</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10491,44 +10457,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10576,25 +10544,25 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>288</v>
+        <v>117</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>445</v>
+        <v>196</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10605,10 +10573,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10619,10 +10587,10 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
@@ -10631,17 +10599,15 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10666,13 +10632,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>77</v>
+        <v>455</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -10690,25 +10656,25 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10719,10 +10685,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10733,10 +10699,10 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>77</v>
@@ -10745,20 +10711,16 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>487</v>
+        <v>321</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10806,35 +10768,1167 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AG78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH78" t="s" s="2">
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI78" t="s" s="2">
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN78">
+  <autoFilter ref="A1:AN88">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10844,7 +11938,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI87">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
